--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N99_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N99_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>29.41647636330111</v>
+        <v>4.780177409036432</v>
       </c>
       <c r="D2" t="n">
-        <v>27.89196559898572</v>
+        <v>4.532444409835179</v>
       </c>
       <c r="E2" t="n">
-        <v>20.62650983018144</v>
+        <v>3.351807847404484</v>
       </c>
       <c r="F2" t="n">
-        <v>21.39743184590017</v>
+        <v>3.477082674958778</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>37.9111811087603</v>
+        <v>6.160566930173549</v>
       </c>
       <c r="D3" t="n">
-        <v>37.08736492625522</v>
+        <v>6.026696800516473</v>
       </c>
       <c r="E3" t="n">
-        <v>20.62650983018144</v>
+        <v>3.351807847404484</v>
       </c>
       <c r="F3" t="n">
-        <v>21.39743184590017</v>
+        <v>3.477082674958778</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>76.79639275037115</v>
+        <v>12.47941382193531</v>
       </c>
       <c r="D4" t="n">
-        <v>77.17645163855917</v>
+        <v>12.54117339126587</v>
       </c>
       <c r="E4" t="n">
-        <v>20.62650983018144</v>
+        <v>3.351807847404484</v>
       </c>
       <c r="F4" t="n">
-        <v>21.39743184590017</v>
+        <v>3.477082674958778</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
